--- a/client/public/booking-template-with-readme.xlsx
+++ b/client/public/booking-template-with-readme.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marinljoljic/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marinljoljic/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8509FB1C-0337-C940-A6C2-892954FA73FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CC8AF6-971A-7C45-846C-ECFBAE6AA167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4940" yWindow="2060" windowWidth="28240" windowHeight="13620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4940" yWindow="2060" windowWidth="28240" windowHeight="13620" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -88,9 +88,6 @@
     <t>End Date</t>
   </si>
   <si>
-    <t>Frequency</t>
-  </si>
-  <si>
     <t>String</t>
   </si>
   <si>
@@ -315,35 +312,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">The system will validate the Frequency field according to the following rules:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Allowed Values</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-The field must be a numeric value.
-The only valid numeric value is 1.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Booking Start Date Validation
 </t>
     </r>
@@ -467,6 +435,38 @@
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Rounds</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The system will validate the Frequency field according to the following rules:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Allowed Values</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The field must be a numeric value.
+</t>
     </r>
   </si>
 </sst>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -928,13 +928,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -942,27 +942,27 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -970,13 +970,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -984,13 +984,13 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="176" x14ac:dyDescent="0.2">
@@ -998,13 +998,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="192" x14ac:dyDescent="0.2">
@@ -1012,27 +1012,27 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
         <v>26</v>
       </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1057,7 +1057,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>17</v>
@@ -1072,21 +1072,21 @@
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2">
         <v>20280118</v>
@@ -1100,16 +1100,16 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3">
         <v>20280121</v>
@@ -1123,16 +1123,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4">
         <v>20280124</v>
@@ -1146,19 +1146,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F5">
         <v>20280127</v>
@@ -1172,16 +1172,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F6">
         <v>20280130</v>
@@ -1195,16 +1195,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F7">
         <v>20280202</v>
@@ -1218,16 +1218,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F8">
         <v>20280205</v>
@@ -1241,19 +1241,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9">
         <v>20280208</v>
@@ -1267,16 +1267,16 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10">
         <v>20280211</v>
@@ -1290,16 +1290,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F11">
         <v>20280214</v>
@@ -1313,16 +1313,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F12">
         <v>20280217</v>
@@ -1336,19 +1336,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13">
         <v>20280220</v>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14">
         <v>20280223</v>
@@ -1385,16 +1385,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>20280226</v>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F16">
         <v>20280229</v>
@@ -1431,19 +1431,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17">
         <v>20280303</v>
@@ -1457,16 +1457,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F18">
         <v>20280306</v>
@@ -1480,16 +1480,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F19">
         <v>20280309</v>
@@ -1503,16 +1503,16 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F20">
         <v>20280312</v>
@@ -1526,19 +1526,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F21">
         <v>20280315</v>
@@ -1578,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>17</v>
@@ -1593,7 +1593,7 @@
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
